--- a/diss/yamb.xlsx
+++ b/diss/yamb.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\PVT_TSU\diss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1AFCD3A-6F6B-447F-A418-312AF5E4CFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C721105C-BCE3-4B55-A2B9-EEADB477C261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12825" yWindow="2955" windowWidth="15375" windowHeight="7875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="to_model" sheetId="2" r:id="rId2"/>
+    <sheet name="test" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="59">
   <si>
     <t>CO2</t>
   </si>
@@ -219,8 +220,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -274,8 +275,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1475,4 +1476,343 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17AB22C1-A8A6-4DF4-A3C5-C438B4CDC725}">
+  <sheetPr codeName="Лист3"/>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>3.0100000000000005E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1.3600000000000001E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.66147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>5.586E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>4.6829999999999997E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7">
+        <v>1.0709999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8">
+        <v>2.479E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9">
+        <v>8.9499999999999996E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10">
+        <v>1.1470000000000001E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>2.6510000000000002E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>2.6680000000000002E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>2.0899999999999998E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14">
+        <v>1.1359999999999999E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15">
+        <v>1.3049999999999999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16">
+        <v>9.5999999999999992E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17">
+        <v>8.1300000000000001E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18">
+        <v>7.6699999999999997E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19">
+        <v>6.1900000000000002E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20">
+        <v>5.7799999999999995E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21">
+        <v>4.4200000000000003E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22">
+        <v>3.8800000000000002E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23">
+        <v>3.6099999999999999E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24">
+        <v>3.0999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25">
+        <v>2.5800000000000003E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
+        <v>2.32E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28">
+        <v>1.81E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29">
+        <v>1.6100000000000001E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30">
+        <v>1.4499999999999999E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31">
+        <v>1.2900000000000001E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32">
+        <v>1.1899999999999999E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33">
+        <v>1.08E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34">
+        <v>1.0299999999999999E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35">
+        <v>9.5E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36">
+        <v>8.699999999999999E-4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37">
+        <v>8.1999999999999998E-4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38">
+        <v>6.6E-4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39">
+        <v>6.7000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40">
+        <v>5.9999999999999995E-4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41">
+        <v>3.7399999999999998E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>